--- a/completed/arylation_10.1021.acscatal.6b00861.xlsx
+++ b/completed/arylation_10.1021.acscatal.6b00861.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/core/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/completed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512C4656-1FC9-6446-A954-86E1695CFF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0523CDF5-8722-4748-BEF2-BB6A4672118B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7240" yWindow="3180" windowWidth="28140" windowHeight="21900" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
+    <workbookView xWindow="7240" yWindow="500" windowWidth="28140" windowHeight="21900" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,9 +95,6 @@
     <t>Frequency (RPM)</t>
   </si>
   <si>
-    <t>SOLVENT</t>
-  </si>
-  <si>
     <t>C/C(C1=CC=CC=C1C2=CC=C(C)C=C2)=N\OC</t>
   </si>
   <si>
@@ -405,6 +402,9 @@
   </si>
   <si>
     <t>w0803284@tamu.edu</t>
+  </si>
+  <si>
+    <t>ADDITIVE</t>
   </si>
 </sst>
 </file>
@@ -1008,16 +1008,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1028,10 +1028,10 @@
       </c>
       <c r="F4" s="13"/>
       <c r="G4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" t="s">
         <v>119</v>
-      </c>
-      <c r="H4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1040,22 +1040,22 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" t="s">
         <v>109</v>
-      </c>
-      <c r="E5" t="s">
-        <v>110</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="18" t="s">
         <v>121</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>122</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -1082,19 +1082,19 @@
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="3" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="3" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>8</v>
@@ -1112,37 +1112,37 @@
         <v>9</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="H8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="J8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="K8" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="L8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" t="s">
         <v>57</v>
-      </c>
-      <c r="M8" t="s">
-        <v>58</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>9</v>
@@ -1182,44 +1182,44 @@
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" s="6">
         <v>0.3</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="6">
         <v>0.6</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10" s="6">
         <v>1.8</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I10" s="6">
         <v>0.6</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K10" s="6">
         <v>0.3</v>
       </c>
       <c r="L10" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M10">
         <f t="shared" ref="M10:M23" si="0">E10*0.1</f>
         <v>0.06</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O10" s="6">
         <v>41.48</v>
@@ -1238,25 +1238,25 @@
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
       <c r="B11" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" s="6">
         <v>0.3</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="6">
         <v>0.6</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" s="6">
         <v>1.8</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I11" s="6">
         <v>0.6</v>
@@ -1264,14 +1264,14 @@
       <c r="J11" s="5"/>
       <c r="K11" s="6"/>
       <c r="L11" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M11">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O11" s="6">
         <v>81.599999999999994</v>
@@ -1290,44 +1290,44 @@
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="15"/>
       <c r="B12" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="6">
         <v>0.3</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="6">
         <v>0.6</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G12" s="6">
         <v>1.8</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I12" s="6">
         <v>0.6</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K12" s="6">
         <v>0.3</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M12">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O12" s="6">
         <v>74.400000000000006</v>
@@ -1346,44 +1346,44 @@
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="6">
         <v>0.3</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="6">
         <v>0.6</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13" s="6">
         <v>1.8</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I13" s="6">
         <v>0.6</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K13" s="6">
         <v>0.3</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M13">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O13" s="6">
         <v>7.52</v>
@@ -1402,44 +1402,44 @@
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="6">
         <v>0.3</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="6">
         <v>0.6</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14" s="6">
         <v>1.8</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I14" s="6">
         <v>0.6</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K14" s="6">
         <v>0.3</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M14">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O14" s="6">
         <v>60.8</v>
@@ -1458,44 +1458,44 @@
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15" s="6">
         <v>0.3</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="6">
         <v>0.6</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15" s="6">
         <v>1.8</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I15" s="6">
         <v>0.6</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K15" s="6">
         <v>0.3</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M15">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O15" s="6">
         <v>48.84</v>
@@ -1514,44 +1514,44 @@
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" s="6">
         <v>0.3</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" s="6">
         <v>0.6</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G16" s="6">
         <v>1.8</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I16" s="6">
         <v>0.6</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K16" s="6">
         <v>0.3</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M16">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O16" s="6">
         <v>15.84</v>
@@ -1570,44 +1570,44 @@
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
       <c r="B17" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="6">
         <v>0.3</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" s="6">
         <v>0.6</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G17" s="6">
         <v>1.8</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I17" s="6">
         <v>0.6</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K17" s="6">
         <v>0.3</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M17">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O17" s="6">
         <v>46.62</v>
@@ -1626,7 +1626,7 @@
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="6">
         <v>0.3</v>
@@ -1638,32 +1638,32 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G18" s="6">
         <v>1.8</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I18" s="6">
         <v>0.6</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K18" s="6">
         <v>0.3</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M18">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O18" s="6">
         <v>33.479999999999997</v>
@@ -1682,44 +1682,44 @@
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
       <c r="B19" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C19" s="6">
         <v>0.3</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" s="6">
         <v>0.6</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G19" s="6">
         <v>1.8</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I19" s="6">
         <v>0.6</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K19" s="6">
         <v>0.3</v>
       </c>
       <c r="L19" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M19">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O19" s="6">
         <v>0</v>
@@ -1738,44 +1738,44 @@
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="15"/>
       <c r="B20" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C20" s="6">
         <v>0.3</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E20" s="6">
         <v>0.6</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G20" s="6">
         <v>1.8</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I20" s="6">
         <v>0.6</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K20" s="6">
         <v>0.3</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M20">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O20" s="6">
         <v>0</v>
@@ -1794,44 +1794,44 @@
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
       <c r="B21" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C21" s="6">
         <v>0.3</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E21" s="6">
         <v>0.6</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G21" s="6">
         <v>1.8</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I21" s="6">
         <v>0.6</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K21" s="6">
         <v>0.3</v>
       </c>
       <c r="L21" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M21">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O21" s="6">
         <v>0</v>
@@ -1850,44 +1850,44 @@
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="15"/>
       <c r="B22" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" s="6">
         <v>0.3</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E22" s="6">
         <v>0.6</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22" s="6">
         <v>1.8</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I22" s="6">
         <v>0.6</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K22" s="6">
         <v>0.3</v>
       </c>
       <c r="L22" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M22">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O22" s="6">
         <v>70.400000000000006</v>
@@ -1906,44 +1906,44 @@
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
       <c r="B23" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="6">
         <v>0.3</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E23" s="6">
         <v>0.6</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G23" s="6">
         <v>1.8</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I23" s="6">
         <v>0.6</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K23" s="6">
         <v>0.3</v>
       </c>
       <c r="L23" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M23">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O23" s="6">
         <v>1.56</v>
@@ -1962,38 +1962,38 @@
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="15"/>
       <c r="B24" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" s="6">
         <v>0.3</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" s="6">
         <v>0.6</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G24" s="6">
         <v>1.8</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I24" s="6">
         <v>0.6</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K24" s="6">
         <v>0.3</v>
       </c>
       <c r="L24" s="17"/>
       <c r="N24" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O24" s="6">
         <v>0</v>
@@ -2012,25 +2012,25 @@
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
       <c r="B25" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25" s="6">
         <v>0.3</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="6">
         <v>0.6</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G25" s="6">
         <v>1.8</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I25" s="6">
         <v>0.3</v>
@@ -2038,14 +2038,14 @@
       <c r="J25" s="5"/>
       <c r="K25" s="6"/>
       <c r="L25" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M25">
         <f t="shared" ref="M25:M65" si="2">E25*0.1</f>
         <v>0.06</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O25" s="6">
         <v>0</v>
@@ -2064,25 +2064,25 @@
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="15"/>
       <c r="B26" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C26" s="6">
         <v>0.3</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" s="6">
         <v>0.6</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G26" s="6">
         <v>0.6</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I26" s="6">
         <v>0.3</v>
@@ -2090,14 +2090,14 @@
       <c r="J26" s="5"/>
       <c r="K26" s="6"/>
       <c r="L26" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M26">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O26" s="6">
         <v>81</v>
@@ -2116,44 +2116,44 @@
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
       <c r="B27" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" s="6">
         <v>0.3</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" s="6">
         <v>0.6</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G27" s="6">
         <v>1.5</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I27" s="6">
         <v>0.6</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K27" s="6">
         <v>0.3</v>
       </c>
       <c r="L27" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M27">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O27" s="6">
         <v>70</v>
@@ -2168,44 +2168,44 @@
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="15"/>
       <c r="B28" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" s="6">
         <v>0.3</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" s="6">
         <v>0.6</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G28" s="6">
         <v>1.8</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I28" s="6">
         <v>0.6</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K28" s="6">
         <v>0.3</v>
       </c>
       <c r="L28" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M28">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O28" s="6">
         <v>65</v>
@@ -2224,44 +2224,44 @@
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
       <c r="B29" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C29" s="6">
         <v>0.3</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" s="6">
         <v>0.6</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G29" s="6">
         <v>0.9</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I29" s="6">
         <v>0.6</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K29" s="6">
         <v>0.3</v>
       </c>
       <c r="L29" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M29">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O29" s="6">
         <v>63</v>
@@ -2280,44 +2280,44 @@
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="15"/>
       <c r="B30" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" s="6">
         <v>0.3</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" s="6">
         <v>0.6</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G30" s="6">
         <v>0.9</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I30" s="6">
         <v>0.6</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K30" s="6">
         <v>0.3</v>
       </c>
       <c r="L30" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M30">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O30" s="6">
         <v>85</v>
@@ -2336,44 +2336,44 @@
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="15"/>
       <c r="B31" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C31" s="6">
         <v>0.3</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" s="6">
         <v>0.6</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G31" s="6">
         <v>0.9</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I31" s="6">
         <v>0.6</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K31" s="6">
         <v>0.3</v>
       </c>
       <c r="L31" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M31">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O31" s="6">
         <v>65</v>
@@ -2392,44 +2392,44 @@
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="15"/>
       <c r="B32" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C32" s="6">
         <v>0.3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E32" s="6">
         <v>0.6</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G32" s="6">
         <v>1.8</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I32" s="6">
         <v>0.6</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K32" s="6">
         <v>0.3</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M32">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O32" s="6">
         <v>52</v>
@@ -2448,44 +2448,44 @@
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="15"/>
       <c r="B33" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C33" s="6">
         <v>0.3</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E33" s="6">
         <v>0.6</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G33" s="6">
         <v>0.9</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I33" s="6">
         <v>0.6</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K33" s="6">
         <v>0.3</v>
       </c>
       <c r="L33" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M33">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O33" s="6">
         <v>75</v>
@@ -2504,44 +2504,44 @@
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="15"/>
       <c r="B34" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C34" s="6">
         <v>0.3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E34" s="6">
         <v>0.6</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G34" s="6">
         <v>0.9</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I34" s="6">
         <v>0.6</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K34" s="6">
         <v>0.3</v>
       </c>
       <c r="L34" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M34">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O34" s="6">
         <v>71</v>
@@ -2560,44 +2560,44 @@
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="15"/>
       <c r="B35" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C35" s="6">
         <v>0.3</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E35" s="6">
         <v>0.6</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G35" s="6">
         <v>0.9</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I35" s="6">
         <v>0.6</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K35" s="6">
         <v>0.3</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M35">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O35" s="6">
         <v>62</v>
@@ -2616,44 +2616,44 @@
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="15"/>
       <c r="B36" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C36" s="6">
         <v>0.3</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36" s="6">
         <v>0.6</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G36" s="6">
         <v>1.5</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I36" s="6">
         <v>0.6</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K36" s="6">
         <v>0.3</v>
       </c>
       <c r="L36" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M36">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O36" s="6">
         <v>59</v>
@@ -2668,44 +2668,44 @@
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="15"/>
       <c r="B37" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C37" s="6">
         <v>0.3</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E37" s="6">
         <v>0.6</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G37" s="6">
         <v>0.9</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I37" s="6">
         <v>0.6</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K37" s="6">
         <v>0.3</v>
       </c>
       <c r="L37" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M37">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O37" s="6">
         <v>79</v>
@@ -2724,44 +2724,44 @@
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="15"/>
       <c r="B38" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C38" s="6">
         <v>0.3</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38" s="6">
         <v>0.6</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G38" s="6">
         <v>1.5</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I38" s="6">
         <v>0.6</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K38" s="6">
         <v>0.3</v>
       </c>
       <c r="L38" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M38">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O38" s="6">
         <v>74</v>
@@ -2776,44 +2776,44 @@
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="15"/>
       <c r="B39" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C39" s="6">
         <v>0.3</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39" s="6">
         <v>0.6</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G39" s="6">
         <v>1.8</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I39" s="6">
         <v>0.6</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K39" s="6">
         <v>0.3</v>
       </c>
       <c r="L39" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M39">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O39" s="6">
         <v>68</v>
@@ -2832,44 +2832,44 @@
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="15"/>
       <c r="B40" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C40" s="6">
         <v>0.3</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E40" s="6">
         <v>0.6</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G40" s="6">
         <v>0.9</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I40" s="6">
         <v>0.6</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K40" s="6">
         <v>0.3</v>
       </c>
       <c r="L40" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M40">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O40" s="6">
         <v>55</v>
@@ -2888,44 +2888,44 @@
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="15"/>
       <c r="B41" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C41" s="6">
         <v>0.3</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E41" s="6">
         <v>0.6</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G41" s="6">
         <v>0.9</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I41" s="6">
         <v>0.6</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K41" s="6">
         <v>0.3</v>
       </c>
       <c r="L41" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M41">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N41" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O41" s="6">
         <v>75</v>
@@ -2944,44 +2944,44 @@
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="15"/>
       <c r="B42" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C42" s="6">
         <v>0.3</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E42" s="6">
         <v>0.6</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G42" s="6">
         <v>0.9</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I42" s="6">
         <v>0.6</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K42" s="6">
         <v>0.3</v>
       </c>
       <c r="L42" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M42">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O42" s="6">
         <v>52</v>
@@ -3000,44 +3000,44 @@
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="15"/>
       <c r="B43" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C43" s="6">
         <v>0.3</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E43" s="6">
         <v>0.6</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G43" s="6">
         <v>0.9</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I43" s="6">
         <v>0.6</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K43" s="6">
         <v>0.3</v>
       </c>
       <c r="L43" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M43">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N43" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O43" s="6">
         <v>67</v>
@@ -3056,44 +3056,44 @@
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="15"/>
       <c r="B44" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C44" s="6">
         <v>0.3</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E44" s="6">
         <v>0.6</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G44" s="6">
         <v>1.8</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I44" s="6">
         <v>0.6</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K44" s="6">
         <v>0.3</v>
       </c>
       <c r="L44" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M44">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N44" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O44" s="6">
         <v>83</v>
@@ -3112,44 +3112,44 @@
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="15"/>
       <c r="B45" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C45" s="6">
         <v>0.3</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E45" s="6">
         <v>0.6</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G45" s="6">
         <v>1.8</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I45" s="6">
         <v>0.6</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K45" s="6">
         <v>0.3</v>
       </c>
       <c r="L45" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M45">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N45" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O45" s="6">
         <v>82</v>
@@ -3168,44 +3168,44 @@
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="15"/>
       <c r="B46" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C46" s="6">
         <v>0.3</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E46" s="6">
         <v>0.6</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G46" s="6">
         <v>1.8</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I46" s="6">
         <v>0.6</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K46" s="6">
         <v>0.3</v>
       </c>
       <c r="L46" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M46">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N46" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O46" s="6">
         <v>58</v>
@@ -3224,44 +3224,44 @@
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="15"/>
       <c r="B47" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C47" s="6">
         <v>0.3</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E47" s="6">
         <v>0.6</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G47" s="6">
         <v>1.8</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I47" s="6">
         <v>0.6</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K47" s="6">
         <v>0.3</v>
       </c>
       <c r="L47" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M47">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N47" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O47" s="6">
         <v>63</v>
@@ -3280,44 +3280,44 @@
     <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="15"/>
       <c r="B48" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C48" s="6">
         <v>0.3</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E48" s="6">
         <v>0.6</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G48" s="6">
         <v>1.8</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I48" s="6">
         <v>0.6</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K48" s="6">
         <v>0.3</v>
       </c>
       <c r="L48" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M48">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N48" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O48" s="6">
         <v>66</v>
@@ -3336,44 +3336,44 @@
     <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="15"/>
       <c r="B49" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C49" s="6">
         <v>0.3</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E49" s="6">
         <v>0.6</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G49" s="6">
         <v>1.8</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I49" s="6">
         <v>0.6</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K49" s="6">
         <v>0.3</v>
       </c>
       <c r="L49" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M49">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N49" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O49" s="6">
         <v>58</v>
@@ -3391,44 +3391,44 @@
     <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="15"/>
       <c r="B50" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C50" s="6">
         <v>0.3</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E50" s="6">
         <v>0.6</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G50" s="6">
         <v>1.8</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I50" s="6">
         <v>0.6</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K50" s="6">
         <v>0.3</v>
       </c>
       <c r="L50" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M50">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N50" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O50" s="6">
         <v>42</v>
@@ -3446,44 +3446,44 @@
     <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="15"/>
       <c r="B51" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C51" s="6">
         <v>0.3</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E51" s="6">
         <v>0.6</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G51" s="6">
         <v>1.8</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I51" s="6">
         <v>0.6</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K51" s="6">
         <v>0.3</v>
       </c>
       <c r="L51" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M51">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N51" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O51" s="6">
         <v>40</v>
@@ -3501,44 +3501,44 @@
     <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="15"/>
       <c r="B52" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C52" s="6">
         <v>0.3</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E52" s="6">
         <v>0.6</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G52" s="6">
         <v>1.8</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I52" s="6">
         <v>0.6</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K52" s="6">
         <v>0.3</v>
       </c>
       <c r="L52" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M52">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N52" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O52" s="6">
         <v>39</v>
@@ -3556,44 +3556,44 @@
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="15"/>
       <c r="B53" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C53" s="6">
         <v>0.3</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E53" s="6">
         <v>0.6</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G53" s="6">
         <v>1.8</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I53" s="6">
         <v>0.6</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K53" s="6">
         <v>0.3</v>
       </c>
       <c r="L53" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M53">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N53" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O53" s="6">
         <v>80</v>
@@ -3612,44 +3612,44 @@
     <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="15"/>
       <c r="B54" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C54" s="6">
         <v>0.3</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E54" s="6">
         <v>0.6</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G54" s="6">
         <v>1.8</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I54" s="6">
         <v>0.6</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K54" s="6">
         <v>0.3</v>
       </c>
       <c r="L54" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M54">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N54" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O54" s="6">
         <v>81</v>
@@ -3668,44 +3668,44 @@
     <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="15"/>
       <c r="B55" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C55" s="6">
         <v>0.3</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E55" s="6">
         <v>0.6</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G55" s="6">
         <v>1.8</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I55" s="6">
         <v>0.6</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K55" s="6">
         <v>0.3</v>
       </c>
       <c r="L55" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M55">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N55" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O55" s="6">
         <v>70</v>
@@ -3724,44 +3724,44 @@
     <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="15"/>
       <c r="B56" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C56" s="6">
         <v>0.3</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E56" s="6">
         <v>0.6</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G56" s="6">
         <v>1.8</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I56" s="6">
         <v>0.6</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K56" s="6">
         <v>0.3</v>
       </c>
       <c r="L56" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M56">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N56" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O56" s="6">
         <v>52</v>
@@ -3780,44 +3780,44 @@
     <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="15"/>
       <c r="B57" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C57" s="6">
         <v>0.3</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E57" s="6">
         <v>0.6</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G57" s="6">
         <v>1.8</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I57" s="6">
         <v>0.6</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K57" s="6">
         <v>0.3</v>
       </c>
       <c r="L57" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M57">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N57" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O57" s="6">
         <v>85</v>
@@ -3836,44 +3836,44 @@
     <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="15"/>
       <c r="B58" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C58" s="6">
         <v>0.3</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E58" s="6">
         <v>0.6</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G58" s="6">
         <v>1.8</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I58" s="6">
         <v>0.6</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K58" s="6">
         <v>0.3</v>
       </c>
       <c r="L58" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M58">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N58" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O58" s="6">
         <v>71</v>
@@ -3892,44 +3892,44 @@
     <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="15"/>
       <c r="B59" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C59" s="6">
         <v>0.3</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E59" s="6">
         <v>0.6</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G59" s="6">
         <v>1.8</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I59" s="6">
         <v>0.6</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K59" s="6">
         <v>0.3</v>
       </c>
       <c r="L59" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M59">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N59" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O59" s="6">
         <v>65</v>
@@ -3948,19 +3948,19 @@
     <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="15"/>
       <c r="B60" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C60" s="6">
         <v>0.3</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E60" s="6">
         <v>0.6</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G60" s="6">
         <v>1.8</v>
@@ -3970,14 +3970,14 @@
       <c r="J60" s="5"/>
       <c r="K60" s="6"/>
       <c r="L60" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M60">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N60" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O60" s="6">
         <v>92</v>
@@ -3996,19 +3996,19 @@
     <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="15"/>
       <c r="B61" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C61" s="6">
         <v>0.3</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E61" s="6">
         <v>0.6</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G61" s="6">
         <v>1.8</v>
@@ -4018,14 +4018,14 @@
       <c r="J61" s="5"/>
       <c r="K61" s="6"/>
       <c r="L61" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M61">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N61" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O61" s="6">
         <v>65</v>
@@ -4044,19 +4044,19 @@
     <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="15"/>
       <c r="B62" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C62" s="6">
         <v>0.3</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E62" s="6">
         <v>0.6</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G62" s="6">
         <v>1.8</v>
@@ -4066,14 +4066,14 @@
       <c r="J62" s="5"/>
       <c r="K62" s="6"/>
       <c r="L62" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M62">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N62" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O62" s="6">
         <v>78</v>
@@ -4092,19 +4092,19 @@
     <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="15"/>
       <c r="B63" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C63" s="6">
         <v>0.3</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E63" s="6">
         <v>0.6</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G63" s="6">
         <v>0.9</v>
@@ -4114,14 +4114,14 @@
       <c r="J63" s="5"/>
       <c r="K63" s="6"/>
       <c r="L63" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M63">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N63" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O63" s="6">
         <v>91</v>
@@ -4140,19 +4140,19 @@
     <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="15"/>
       <c r="B64" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C64" s="6">
         <v>0.3</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E64" s="6">
         <v>0.6</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G64" s="6">
         <v>0.9</v>
@@ -4162,14 +4162,14 @@
       <c r="J64" s="5"/>
       <c r="K64" s="6"/>
       <c r="L64" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M64">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N64" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O64" s="6">
         <v>60</v>
@@ -4188,19 +4188,19 @@
     <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="15"/>
       <c r="B65" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C65" s="8">
         <v>0.3</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E65" s="8">
         <v>0.6</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G65" s="8">
         <v>0.9</v>
@@ -4210,14 +4210,14 @@
       <c r="J65" s="7"/>
       <c r="K65" s="8"/>
       <c r="L65" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M65">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
       <c r="N65" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O65" s="8">
         <v>54</v>
